--- a/Assets/Data/Excel/BuildingData.xlsx
+++ b/Assets/Data/Excel/BuildingData.xlsx
@@ -12,9 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
-  <si>
-    <t>实例名</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+  <si>
+    <t>#实例名</t>
   </si>
   <si>
     <t>Id</t>
@@ -71,6 +71,9 @@
     <t>buildingSkills</t>
   </si>
   <si>
+    <t>#类型</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -104,7 +107,7 @@
     <t>String[]</t>
   </si>
   <si>
-    <t>实例名称</t>
+    <t>#注释</t>
   </si>
   <si>
     <t/>
@@ -143,7 +146,13 @@
     <t>Block</t>
   </si>
   <si>
+    <t>spe</t>
+  </si>
+  <si>
     <t>NewInstance</t>
+  </si>
+  <si>
+    <t>NewInstance1</t>
   </si>
 </sst>
 </file>
@@ -189,7 +198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -256,158 +265,158 @@
         <v>19</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>19</v>
-      </c>
       <c r="I2" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="0" t="s">
-        <v>22</v>
-      </c>
       <c r="M2" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N2" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O2" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q2" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R2" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S2" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N3" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O3" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P3" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q3" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R3" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S3" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="0">
         <v>60</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L4" s="0">
         <v>10</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N4" s="0">
         <v>100</v>
@@ -422,51 +431,51 @@
         <v>0</v>
       </c>
       <c r="R4" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S4" s="0" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="0">
         <v>60</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L5" s="0">
         <v>10</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N5" s="0">
         <v>100</v>
@@ -481,10 +490,69 @@
         <v>0</v>
       </c>
       <c r="R5" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S5" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="0">
+        <v>60</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="0">
+        <v>10</v>
+      </c>
+      <c r="M6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="0">
+        <v>100</v>
+      </c>
+      <c r="O6" s="0">
+        <v>0</v>
+      </c>
+      <c r="P6" s="0">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="S6" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Excel/BuildingData.xlsx
+++ b/Assets/Data/Excel/BuildingData.xlsx
@@ -89,7 +89,7 @@
     <t>ResourceCost[]</t>
   </si>
   <si>
-    <t>Dictionary`2</t>
+    <t>Dictionary&lt;string,int&gt;</t>
   </si>
   <si>
     <t>BuildingLevelData[]</t>
@@ -104,7 +104,7 @@
     <t>ResourceType</t>
   </si>
   <si>
-    <t>String[]</t>
+    <t>string[]</t>
   </si>
   <si>
     <t>#注释</t>
@@ -146,7 +146,7 @@
     <t>Block</t>
   </si>
   <si>
-    <t>spe</t>
+    <t>spe|gg</t>
   </si>
   <si>
     <t>NewInstance</t>

--- a/Assets/Data/Excel/BuildingData.xlsx
+++ b/Assets/Data/Excel/BuildingData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>#实例名</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>Top.ResourceCost</t>
+  </si>
+  <si>
+    <t>22=22|ss=33</t>
   </si>
   <si>
     <t>Top.BuildingLevelData</t>
@@ -410,13 +413,13 @@
         <v>41</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L4" s="0">
         <v>10</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N4" s="0">
         <v>100</v>
@@ -431,15 +434,15 @@
         <v>0</v>
       </c>
       <c r="R4" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S4" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>32</v>
@@ -490,7 +493,7 @@
         <v>0</v>
       </c>
       <c r="R5" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S5" s="0" t="s">
         <v>32</v>
@@ -498,7 +501,7 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>32</v>
@@ -549,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S6" s="0" t="s">
         <v>32</v>

--- a/Assets/Data/Excel/BuildingData.xlsx
+++ b/Assets/Data/Excel/BuildingData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
   <si>
     <r>
       <rPr>
@@ -53,12 +53,12 @@
     <t xml:space="preserve">IconPath</t>
   </si>
   <si>
+    <t xml:space="preserve">buildingType</t>
+  </si>
+  <si>
     <t xml:space="preserve">size</t>
   </si>
   <si>
-    <t xml:space="preserve">prefabPath</t>
-  </si>
-  <si>
     <t xml:space="preserve">buildTime</t>
   </si>
   <si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t xml:space="preserve">isResourceProducer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">producedResource</t>
   </si>
   <si>
     <t xml:space="preserve">buildingSkills</t>
@@ -105,6 +108,9 @@
     <t xml:space="preserve">string</t>
   </si>
   <si>
+    <t xml:space="preserve">Top.BuildingType</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vector2Int</t>
   </si>
   <si>
@@ -118,6 +124,9 @@
   </si>
   <si>
     <t xml:space="preserve">bool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top.ResourceType</t>
   </si>
   <si>
     <t xml:space="preserve">string[]</t>
@@ -160,19 +169,46 @@
     <t xml:space="preserve">111</t>
   </si>
   <si>
+    <t xml:space="preserve">s11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">asdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource</t>
+  </si>
+  <si>
     <t xml:space="preserve">(2, 2)</t>
   </si>
   <si>
     <t xml:space="preserve">22=22|ss=33|s2=3</t>
   </si>
   <si>
+    <t xml:space="preserve">Block</t>
+  </si>
+  <si>
     <t xml:space="preserve">spe|gg</t>
   </si>
   <si>
     <t xml:space="preserve">NewInstance</t>
   </si>
   <si>
+    <t xml:space="preserve">s22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sdaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22=22|ss=33|s2=4</t>
+  </si>
+  <si>
     <t xml:space="preserve">NewInstance1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22=22|ss=33|s2=5</t>
   </si>
 </sst>
 </file>
@@ -391,8 +427,9 @@
   <dimension ref="A1:S6"/>
   <sheetFormatPr defaultColWidth="8.01171875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="16.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -411,13 +448,13 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
@@ -441,65 +478,69 @@
       <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="S1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="R2" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="S2" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -509,38 +550,46 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
       <c r="S3" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="n">
@@ -548,7 +597,7 @@
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>10</v>
@@ -567,29 +616,41 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="R4" s="2"/>
+      <c r="R4" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="S4" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="F5" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="n">
         <v>60</v>
       </c>
       <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="K5" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="L5" s="2" t="n">
         <v>10</v>
       </c>
@@ -607,27 +668,39 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
+      <c r="R5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="F6" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="G6" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="n">
         <v>60</v>
       </c>
       <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="K6" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="L6" s="2" t="n">
         <v>10</v>
       </c>
@@ -645,8 +718,12 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
+      <c r="R6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Assets/Data/Excel/BuildingData.xlsx
+++ b/Assets/Data/Excel/BuildingData.xlsx
@@ -36,6 +36,7 @@
         <sz val="11"/>
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">实例名</t>
     </r>
@@ -100,11 +101,15 @@
         <sz val="11"/>
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">类型</t>
     </r>
   </si>
   <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
     <t xml:space="preserve">string</t>
   </si>
   <si>
@@ -112,9 +117,6 @@
   </si>
   <si>
     <t xml:space="preserve">Vector2Int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int</t>
   </si>
   <si>
     <t xml:space="preserve">Dictionary&lt;string,int&gt;</t>
@@ -146,6 +148,7 @@
         <sz val="11"/>
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">注释</t>
     </r>
@@ -223,6 +226,7 @@
       <sz val="11"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -288,16 +292,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -427,301 +435,301 @@
   <dimension ref="A1:S6"/>
   <sheetFormatPr defaultColWidth="8.01171875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="H1" s="2"/>
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1" t="s">
+      <c r="J1" s="2"/>
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1" t="s">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="J2" s="2"/>
+      <c r="K2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="M2" s="2"/>
+      <c r="N2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P2" s="1" t="s">
+      <c r="O2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="2" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2" t="s">
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2" t="s">
+      <c r="M3" s="3"/>
+      <c r="N3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2" t="s">
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2" t="n">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="1" t="s">
+      <c r="J4" s="3"/>
+      <c r="K4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="n">
+      <c r="M4" s="3"/>
+      <c r="N4" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="Q4" s="1" t="b">
+      <c r="Q4" s="2" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="R4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="S4" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>222</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="1" t="s">
+      <c r="E5" s="3"/>
+      <c r="F5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2" t="n">
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="1" t="s">
+      <c r="J5" s="3"/>
+      <c r="K5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="n">
+      <c r="M5" s="3"/>
+      <c r="N5" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="P5" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="Q5" s="1" t="b">
+      <c r="Q5" s="2" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="R5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="S5" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>333</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="1" t="s">
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2" t="n">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="1" t="s">
+      <c r="J6" s="3"/>
+      <c r="K6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2" t="n">
+      <c r="M6" s="3"/>
+      <c r="N6" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="P6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" s="1" t="b">
+      <c r="Q6" s="2" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="R6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="S6" s="2" t="s">
         <v>39</v>
       </c>
     </row>

--- a/Assets/Data/Excel/BuildingData.xlsx
+++ b/Assets/Data/Excel/BuildingData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
     <r>
       <rPr>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">costs</t>
   </si>
   <si>
-    <t xml:space="preserve">maxLevel</t>
+    <t xml:space="preserve">levelIdl</t>
   </si>
   <si>
     <t xml:space="preserve">hitPoints</t>
@@ -184,7 +184,7 @@
     <t xml:space="preserve">(2, 2)</t>
   </si>
   <si>
-    <t xml:space="preserve">22=22|ss=33|s2=3</t>
+    <t xml:space="preserve">1|2</t>
   </si>
   <si>
     <t xml:space="preserve">Block</t>
@@ -202,16 +202,10 @@
     <t xml:space="preserve">sdaf</t>
   </si>
   <si>
-    <t xml:space="preserve">22=22|ss=33|s2=4</t>
-  </si>
-  <si>
     <t xml:space="preserve">NewInstance1</t>
   </si>
   <si>
     <t xml:space="preserve">s33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22=22|ss=33|s2=5</t>
   </si>
 </sst>
 </file>
@@ -604,11 +598,9 @@
         <v>60</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="2"/>
+      <c r="L4" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>10</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3" t="n">
@@ -656,11 +648,9 @@
         <v>60</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="K5" s="2"/>
       <c r="L5" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3" t="n">
@@ -685,13 +675,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>333</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -706,11 +696,9 @@
         <v>60</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3" t="n">

--- a/Assets/Data/Excel/BuildingData.xlsx
+++ b/Assets/Data/Excel/BuildingData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
   <si>
     <r>
       <rPr>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">costs</t>
   </si>
   <si>
-    <t xml:space="preserve">levelIdl</t>
+    <t xml:space="preserve">levelId</t>
   </si>
   <si>
     <t xml:space="preserve">hitPoints</t>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t xml:space="preserve">Dictionary&lt;string,int&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int[]</t>
   </si>
   <si>
     <t xml:space="preserve">float</t>
@@ -426,7 +429,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S1048576"/>
   <sheetFormatPr defaultColWidth="8.01171875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.97"/>
@@ -518,7 +521,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
@@ -528,21 +531,21 @@
         <v>17</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -552,46 +555,46 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="n">
@@ -600,7 +603,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="2"/>
       <c r="L4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3" t="n">
@@ -617,31 +620,31 @@
         <v>0</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>222</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3" t="n">
@@ -667,29 +670,29 @@
         <v>0</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>333</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3" t="n">
@@ -715,12 +718,13 @@
         <v>0</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Assets/Data/Excel/BuildingData.xlsx
+++ b/Assets/Data/Excel/BuildingData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <r>
       <rPr>
@@ -60,22 +60,7 @@
     <t xml:space="preserve">size</t>
   </si>
   <si>
-    <t xml:space="preserve">buildTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">costs</t>
-  </si>
-  <si>
     <t xml:space="preserve">levelId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hitPoints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">armor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range</t>
   </si>
   <si>
     <t xml:space="preserve">isResourceProducer</t>
@@ -119,13 +104,7 @@
     <t xml:space="preserve">Vector2Int</t>
   </si>
   <si>
-    <t xml:space="preserve">Dictionary&lt;string,int&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">int[]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">float</t>
   </si>
   <si>
     <t xml:space="preserve">bool</t>
@@ -157,13 +136,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">建造信息</t>
-  </si>
-  <si>
     <t xml:space="preserve">升级信息</t>
-  </si>
-  <si>
-    <t xml:space="preserve">特殊属性</t>
   </si>
   <si>
     <t xml:space="preserve">建筑技能</t>
@@ -429,12 +402,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S1048576"/>
+  <dimension ref="A1:M1048576"/>
   <sheetFormatPr defaultColWidth="8.01171875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="0" width="10.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -470,82 +442,50 @@
       <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -555,173 +495,121 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3" t="s">
-        <v>31</v>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H4" s="3"/>
-      <c r="I4" s="3" t="n">
-        <v>60</v>
+      <c r="I4" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q4" s="2" t="b">
+      <c r="K4" s="2" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="R4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>40</v>
+      <c r="L4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>222</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="2" t="b">
+      <c r="K5" s="2" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="R5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>40</v>
+      <c r="L5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>333</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q6" s="2" t="b">
+      <c r="K6" s="2" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="R6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>40</v>
+      <c r="L6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/Assets/Data/Excel/BuildingData.xlsx
+++ b/Assets/Data/Excel/BuildingData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
   <si>
     <r>
       <rPr>
@@ -54,7 +54,7 @@
     <t xml:space="preserve">IconPath</t>
   </si>
   <si>
-    <t xml:space="preserve">buildingType</t>
+    <t xml:space="preserve">unitTags</t>
   </si>
   <si>
     <t xml:space="preserve">size</t>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t xml:space="preserve">buildingSkills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isDecoration</t>
   </si>
   <si>
     <r>
@@ -98,7 +101,7 @@
     <t xml:space="preserve">string</t>
   </si>
   <si>
-    <t xml:space="preserve">Top.BuildingType</t>
+    <t xml:space="preserve">Top.UnitType[]</t>
   </si>
   <si>
     <t xml:space="preserve">Vector2Int</t>
@@ -402,11 +405,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M1048576"/>
+  <dimension ref="A1:O1048576"/>
   <sheetFormatPr defaultColWidth="8.01171875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="0" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="1" width="10.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -445,47 +448,53 @@
       <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="O1" s="0" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="0" t="s">
         <v>18</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -495,40 +504,40 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="2" t="b">
@@ -536,31 +545,35 @@
         <v>0</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="O4" s="2" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>222</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3" t="n">
@@ -572,29 +585,33 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>333</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3" t="n">
@@ -606,10 +623,14 @@
         <v>0</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/Assets/Data/Excel/BuildingData.xlsx
+++ b/Assets/Data/Excel/BuildingData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
   <si>
     <r>
       <rPr>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">string</t>
   </si>
   <si>
-    <t xml:space="preserve">Top.UnitType[]</t>
+    <t xml:space="preserve">string[]</t>
   </si>
   <si>
     <t xml:space="preserve">Vector2Int</t>
@@ -114,9 +114,6 @@
   </si>
   <si>
     <t xml:space="preserve">Top.ResourceType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string[]</t>
   </si>
   <si>
     <r>
@@ -448,7 +445,7 @@
       <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -486,15 +483,15 @@
         <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -504,40 +501,40 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="2" t="b">
@@ -545,10 +542,10 @@
         <v>0</v>
       </c>
       <c r="L4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="O4" s="2" t="b">
         <f aca="false">FALSE()</f>
@@ -557,23 +554,23 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>222</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3" t="n">
@@ -585,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="O5" s="2" t="n">
         <f aca="false">FALSE()</f>
@@ -597,21 +594,21 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>333</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3" t="n">
@@ -623,10 +620,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="O6" s="2" t="n">
         <f aca="false">FALSE()</f>
